--- a/data/trans_dic/IP12_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023</t>
+          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 12,11</t>
+          <t>1,24; 11,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 20,3</t>
+          <t>5,69; 20,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 13,64</t>
+          <t>4,17; 13,32</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,64</t>
+          <t>3,2; 6,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,52</t>
+          <t>3,63; 7,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,36</t>
+          <t>3,84; 6,46</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,69</t>
+          <t>2,97; 8,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,68</t>
+          <t>3,68; 10,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,57</t>
+          <t>3,91; 8,7</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,43</t>
+          <t>3,59; 6,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,95</t>
+          <t>4,43; 7,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,7</t>
+          <t>4,48; 6,68</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6831</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9556</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>676; 6178</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3531; 12495</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4866; 15539</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>21927</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27061</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48988</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>14725; 30945</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18779; 39140</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37531; 63090</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7898</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11643</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19542</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4441; 12566</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6742; 19720</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13001; 28979</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>32551</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45535</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78086</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>23837; 42996</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>33747; 58792</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>63871; 95229</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,3</t>
+          <t>1,22; 12,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 20,15</t>
+          <t>5,8; 20,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,17; 13,32</t>
+          <t>4,62; 13,32</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,73</t>
+          <t>3,25; 6,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,58</t>
+          <t>3,65; 7,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,46</t>
+          <t>3,85; 6,44</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 8,4</t>
+          <t>2,96; 8,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,76</t>
+          <t>3,61; 10,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,7</t>
+          <t>3,93; 8,48</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,48</t>
+          <t>3,75; 6,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,72</t>
+          <t>4,54; 7,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,68</t>
+          <t>4,55; 6,62</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por síntomas 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>676; 6178</t>
+          <t>668; 6615</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3531; 12495</t>
+          <t>3594; 12671</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4866; 15539</t>
+          <t>5394; 15547</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14725; 30945</t>
+          <t>14948; 30034</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18779; 39140</t>
+          <t>18834; 37529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37531; 63090</t>
+          <t>37598; 62848</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4441; 12566</t>
+          <t>4424; 13051</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6742; 19720</t>
+          <t>6625; 19320</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13001; 28979</t>
+          <t>13084; 28237</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23837; 42996</t>
+          <t>24916; 43140</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33747; 58792</t>
+          <t>34598; 59646</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63871; 95229</t>
+          <t>64839; 94421</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 12,1</t>
+          <t>5,99; 21,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 20,44</t>
+          <t>1,47; 13,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 13,32</t>
+          <t>4,98; 14,86</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,53</t>
+          <t>3,6; 7,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,26</t>
+          <t>3,52; 6,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,44</t>
+          <t>3,99; 6,58</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,73</t>
+          <t>3,33; 10,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,54</t>
+          <t>2,87; 8,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 8,48</t>
+          <t>3,89; 8,47</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,5</t>
+          <t>4,51; 8,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,83</t>
+          <t>3,86; 6,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 6,62</t>
+          <t>4,58; 6,91</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2725</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>9217</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>668; 6615</t>
+          <t>3399; 12392</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3594; 12671</t>
+          <t>689; 6393</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5394; 15547</t>
+          <t>5158; 15375</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>25021</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>46346</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14948; 30034</t>
+          <t>17120; 35955</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18834; 37529</t>
+          <t>15197; 29639</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37598; 62848</t>
+          <t>36239; 59665</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>8073</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>18705</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4424; 13051</t>
+          <t>5616; 17697</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6625; 19320</t>
+          <t>4303; 13249</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13084; 28237</t>
+          <t>12383; 26979</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>42278</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>74268</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24916; 43140</t>
+          <t>31638; 56786</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34598; 59646</t>
+          <t>24283; 41477</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64839; 94421</t>
+          <t>60910; 91909</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R2_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5,99; 21,84</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 13,67</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4,98; 14,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>3,6; 7,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3,52; 6,87</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3,99; 6,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3,33; 10,51</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,87; 8,83</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3,89; 8,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,09%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4,51; 8,1</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3,86; 6,6</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4,58; 6,91</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.116769162733198</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.05544136169190904</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.08906072938318806</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6625</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2592</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9217</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.05991855863052883</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01473493530908065</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.04984236824696178</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3399; 12392</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>689; 6393</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5158; 15375</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.218422693852831</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1367308638589565</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1485638501269039</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.05260145588462667</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.04940729170264956</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05108196141000994</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>25021</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21324</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>46346</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.03599054586800112</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.03521068537135198</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.03994275632445784</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>17120; 35955</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>15197; 29639</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36239; 59665</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.07558782858999048</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.06867250367377455</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.06576299957281073</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.06312587429769134</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.05383146048477231</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.05874784566881061</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10632</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8073</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18705</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.03334556279027184</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.02869410316769281</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.03889084173692041</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5616; 17697</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4303; 13249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12383; 26979</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1050743789708573</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.08834022142723603</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.08473426209405936</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.06032501417363244</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05091231494639981</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.05587535130346836</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>42278</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>31990</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>74268</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.04514342148206218</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.03864625466034632</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.04582605832470088</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>31638; 56786</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>24283; 41477</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>60910; 91909</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.08102688993581103</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.0660108345555341</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.06914772060494581</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por síntomas (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>6625</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2592</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>9217</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3399</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>689</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>5158</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>12392</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6393</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>15375</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>25021</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>21324</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>17120</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>15197</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>36239</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>35955</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>29639</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>59665</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>10632</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>8073</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>18705</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>5616</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>4303</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>12383</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>17697</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>13249</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>26979</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>42278</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>31990</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>74268</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>31638</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>24283</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>60910</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>56786</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>41477</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>91909</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>